--- a/PE/ext_Resources/database/pe_database.xlsx
+++ b/PE/ext_Resources/database/pe_database.xlsx
@@ -1,32 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CSharpe-PE\PE\ext_Resources\file\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Automotive_Software_DET5\PESAT\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{883BA88E-01A1-4561-8A33-64B3F330413D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" firstSheet="1" activeTab="10" xr2:uid="{F46F73B6-9C4F-47DE-B779-0A6401A94E00}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="7.4kW_CCU_L" sheetId="11" r:id="rId1"/>
     <sheet name="7.4kW_CCU_S" sheetId="10" r:id="rId2"/>
-    <sheet name="22kW_CCU_L" sheetId="3" r:id="rId3"/>
-    <sheet name="DAI_OBC" sheetId="4" r:id="rId4"/>
-    <sheet name="DAI_DCB1.2" sheetId="1" r:id="rId5"/>
-    <sheet name="DAI_DCB1.2H" sheetId="5" r:id="rId6"/>
-    <sheet name="DAI_DCB2.0" sheetId="6" r:id="rId7"/>
-    <sheet name="REN_5DH" sheetId="7" r:id="rId8"/>
-    <sheet name="NISSAN_OBC" sheetId="8" r:id="rId9"/>
-    <sheet name="POR_IPB" sheetId="12" r:id="rId10"/>
-    <sheet name="BJB" sheetId="13" r:id="rId11"/>
-    <sheet name="CUSTOM" sheetId="9" r:id="rId12"/>
+    <sheet name="11kW_CCU_S" sheetId="15" r:id="rId3"/>
+    <sheet name="22kW_CCU_L" sheetId="3" r:id="rId4"/>
+    <sheet name="DAI_OBC" sheetId="4" r:id="rId5"/>
+    <sheet name="DAI_DCB1.2" sheetId="1" r:id="rId6"/>
+    <sheet name="DAI_DCB1.2H" sheetId="5" r:id="rId7"/>
+    <sheet name="DAI_DCB2.0" sheetId="6" r:id="rId8"/>
+    <sheet name="DAI_DCB2.0 CR68" sheetId="14" r:id="rId9"/>
+    <sheet name="REN_5DH" sheetId="7" r:id="rId10"/>
+    <sheet name="NISSAN_OBC" sheetId="8" r:id="rId11"/>
+    <sheet name="POR_IPB" sheetId="12" r:id="rId12"/>
+    <sheet name="BJB" sheetId="13" r:id="rId13"/>
+    <sheet name="CUSTOM" sheetId="9" r:id="rId14"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="81">
   <si>
     <t>Contact Pairs</t>
   </si>
@@ -267,12 +268,24 @@
   </si>
   <si>
     <t>P2 to P4(RE)</t>
+  </si>
+  <si>
+    <t>MPEC1 to MPE</t>
+  </si>
+  <si>
+    <t>MPEC2 to MPE</t>
+  </si>
+  <si>
+    <t>MPEC1 to MPE (RE)</t>
+  </si>
+  <si>
+    <t>MPEC2 to MPE (RE)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1">
     <font>
       <sz val="11"/>
@@ -368,7 +381,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{4C909737-61F7-4F49-A89A-6D335BD6DD85}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -677,7 +690,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C833A5FB-9A69-44F9-A380-760933D3676C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D9"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
@@ -779,7 +792,80 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE7BEE4B-FDF7-41CA-8786-21DB77BD0730}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="14.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B2" s="8">
+        <v>20</v>
+      </c>
+      <c r="C2" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="D2" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B3" s="8">
+        <v>20</v>
+      </c>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4" s="8">
+        <v>20</v>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" s="8">
+        <v>20</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
@@ -823,8 +909,53 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDB57177-9F19-4321-BE5B-81F7E67865CE}">
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B2" s="5">
+        <v>10</v>
+      </c>
+      <c r="C2" s="6">
+        <v>5</v>
+      </c>
+      <c r="D2" s="7">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
@@ -908,8 +1039,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FD0778F-CE7F-4479-A4FA-B54BCE8E62E6}">
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
@@ -955,7 +1086,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D1F2C6A-CE59-487B-BA95-DCC95811EF13}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D9"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
@@ -1057,7 +1188,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C25B58C-B2FA-47E7-BFF1-8BC18104189A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D9"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
@@ -1159,7 +1290,109 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5B3C947-D757-45AA-817A-4B43C428C667}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="5">
+        <v>10</v>
+      </c>
+      <c r="C2" s="6">
+        <v>5</v>
+      </c>
+      <c r="D2" s="7">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="5">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -1412,8 +1645,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1E4A438-F966-48A2-AFD5-D9139D663046}">
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D41"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
@@ -1769,8 +2002,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06C5E0E7-8060-4401-A9FF-74A0D7403DC3}">
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
@@ -1814,8 +2047,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BECD227B-6E8F-43BD-BC3F-E2F60B91D590}">
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D9"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
@@ -1915,85 +2148,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{603C8D41-01FC-4D0E-92B9-31FA79835127}">
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="30.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="14.140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B2" s="8">
-        <v>20</v>
-      </c>
-      <c r="C2" s="6">
-        <v>0.02</v>
-      </c>
-      <c r="D2" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B3" s="8">
-        <v>20</v>
-      </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="B4" s="8">
-        <v>20</v>
-      </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="B5" s="8">
-        <v>20</v>
-      </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A96459A-EFE5-49DC-B9F0-72C636BBE5E1}">
-  <dimension ref="A1:D2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -2016,16 +2176,104 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="5" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B2" s="5">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C2" s="6">
         <v>5</v>
       </c>
       <c r="D2" s="7">
         <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B3" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B6" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B7" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B12" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" s="5">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
